--- a/apps/sierra-estates-realty/public/downloads/sierra-estates-unknown-broker-owner.xlsx
+++ b/apps/sierra-estates-realty/public/downloads/sierra-estates-unknown-broker-owner.xlsx
@@ -1212,7 +1212,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V12" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.533Z</v>
       </c>
     </row>
     <row r="13">
@@ -1280,7 +1280,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V13" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.533Z</v>
       </c>
     </row>
     <row r="14">
@@ -1416,7 +1416,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V15" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.533Z</v>
       </c>
     </row>
     <row r="16">
@@ -2028,7 +2028,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V24" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.533Z</v>
       </c>
     </row>
     <row r="25">
@@ -2096,7 +2096,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V25" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.533Z</v>
       </c>
     </row>
     <row r="26">
@@ -2368,7 +2368,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V29" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.533Z</v>
       </c>
     </row>
     <row r="30">
@@ -2912,7 +2912,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V37" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="38">
@@ -3116,7 +3116,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V40" t="str">
-        <v>2026-09-04T14:50:11.467Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="41">
@@ -3252,7 +3252,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V42" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="43">
@@ -3320,7 +3320,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V43" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="44">
@@ -3388,7 +3388,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V44" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="45">
@@ -3524,7 +3524,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V46" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="47">
@@ -3932,7 +3932,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V52" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="53">
@@ -4340,7 +4340,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V58" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="59">
@@ -4544,7 +4544,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V61" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="62">
@@ -4884,7 +4884,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V66" t="str">
-        <v>2026-09-04T14:50:11.468Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="67">
@@ -6652,7 +6652,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V92" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="93">
@@ -6720,7 +6720,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V93" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.534Z</v>
       </c>
     </row>
     <row r="94">
@@ -7264,7 +7264,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V101" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="102">
@@ -7332,7 +7332,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V102" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="103">
@@ -7944,7 +7944,7 @@
         <v>Master</v>
       </c>
       <c r="V111" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="112">
@@ -8148,7 +8148,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V114" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="115">
@@ -8420,7 +8420,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V118" t="str">
-        <v>2026-09-04T14:50:11.469Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="119">
@@ -8964,7 +8964,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V126" t="str">
-        <v>2026-09-04T14:50:11.470Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="127">
@@ -9576,7 +9576,7 @@
         <v>Master</v>
       </c>
       <c r="V135" t="str">
-        <v>2026-09-04T14:50:11.470Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="136">
@@ -9644,7 +9644,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V136" t="str">
-        <v>2026-09-04T14:50:11.470Z</v>
+        <v>2026-09-07T03:58:05.535Z</v>
       </c>
     </row>
     <row r="137">
@@ -10868,7 +10868,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V154" t="str">
-        <v>2026-09-04T14:50:11.470Z</v>
+        <v>2026-09-07T03:58:05.536Z</v>
       </c>
     </row>
     <row r="155">
@@ -11004,7 +11004,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V156" t="str">
-        <v>2026-09-04T14:50:11.470Z</v>
+        <v>2026-09-07T03:58:05.536Z</v>
       </c>
     </row>
     <row r="157">
@@ -11684,7 +11684,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V166" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.536Z</v>
       </c>
     </row>
     <row r="167">
@@ -11820,7 +11820,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V168" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.536Z</v>
       </c>
     </row>
     <row r="169">
@@ -12432,7 +12432,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V177" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.536Z</v>
       </c>
     </row>
     <row r="178">
@@ -12570,7 +12570,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V179" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="180">
@@ -12638,7 +12638,7 @@
         <v>Master</v>
       </c>
       <c r="V180" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="181">
@@ -12978,7 +12978,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V185" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="186">
@@ -13046,7 +13046,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V186" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="187">
@@ -13114,7 +13114,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V187" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="188">
@@ -13182,7 +13182,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V188" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="189">
@@ -13590,7 +13590,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V194" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="195">
@@ -13930,7 +13930,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V199" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="200">
@@ -13998,7 +13998,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V200" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="201">
@@ -14066,7 +14066,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V201" t="str">
-        <v>2026-09-04T14:50:11.471Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="202">
@@ -14202,7 +14202,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V203" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="204">
@@ -14338,7 +14338,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V205" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.537Z</v>
       </c>
     </row>
     <row r="206">
@@ -14406,7 +14406,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V206" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="207" xml:space="preserve">
@@ -14475,7 +14475,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V207" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="208">
@@ -14611,7 +14611,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V209" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="210">
@@ -14679,7 +14679,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V210" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="211">
@@ -14815,7 +14815,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V212" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="213">
@@ -15087,7 +15087,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V216" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="217">
@@ -15359,7 +15359,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V220" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="221">
@@ -15563,7 +15563,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V223" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="224">
@@ -15631,7 +15631,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V224" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="225">
@@ -15903,7 +15903,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V228" t="str">
-        <v>2026-09-04T14:50:11.472Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="229">
@@ -16107,7 +16107,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V231" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="232">
@@ -16175,7 +16175,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V232" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="233">
@@ -16379,7 +16379,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V235" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="236" xml:space="preserve">
@@ -16449,7 +16449,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V236" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="237">
@@ -16517,7 +16517,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V237" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="238">
@@ -16789,7 +16789,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V241" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="242">
@@ -16857,7 +16857,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V242" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="243">
@@ -16925,7 +16925,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V243" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="244">
@@ -17061,7 +17061,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V245" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="246">
@@ -17333,7 +17333,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V249" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="250">
@@ -17401,7 +17401,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V250" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="251">
@@ -17605,7 +17605,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V253" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="254">
@@ -17741,7 +17741,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V255" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="256">
@@ -17877,7 +17877,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V257" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="258">
@@ -18013,7 +18013,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V259" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="260">
@@ -18081,7 +18081,7 @@
         <v>Master</v>
       </c>
       <c r="V260" t="str">
-        <v>2026-09-04T14:50:11.473Z</v>
+        <v>2026-09-07T03:58:05.538Z</v>
       </c>
     </row>
     <row r="261">
@@ -18557,7 +18557,7 @@
         <v>Master</v>
       </c>
       <c r="V267" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="268">
@@ -18693,7 +18693,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V269" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="270">
@@ -18761,7 +18761,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V270" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="271">
@@ -18829,7 +18829,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V271" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="272">
@@ -19101,7 +19101,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V275" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="276">
@@ -19305,7 +19305,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V278" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="279">
@@ -19713,7 +19713,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V284" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="285">
@@ -19849,7 +19849,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V286" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="287">
@@ -20053,7 +20053,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V289" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="290">
@@ -20121,7 +20121,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V290" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="291">
@@ -20189,7 +20189,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V291" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="292">
@@ -20257,7 +20257,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V292" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="293">
@@ -20393,7 +20393,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V294" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="295">
@@ -20461,7 +20461,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V295" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="296">
@@ -20665,7 +20665,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V298" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="299">
@@ -20801,7 +20801,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V300" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="301">
@@ -20869,7 +20869,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V301" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="302">
@@ -20937,7 +20937,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V302" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="303">
@@ -21005,7 +21005,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V303" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="304">
@@ -21073,7 +21073,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V304" t="str">
-        <v>2026-09-04T14:50:11.474Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="305">
@@ -21141,7 +21141,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V305" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="306">
@@ -21209,7 +21209,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V306" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="307">
@@ -21345,7 +21345,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V308" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="309">
@@ -21481,7 +21481,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V310" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="311">
@@ -21617,7 +21617,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V312" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="313">
@@ -21685,7 +21685,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V313" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="314">
@@ -21821,7 +21821,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V315" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="316">
@@ -21889,7 +21889,7 @@
         <v>Master</v>
       </c>
       <c r="V316" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="317">
@@ -21957,7 +21957,7 @@
         <v>Master</v>
       </c>
       <c r="V317" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="318">
@@ -22025,7 +22025,7 @@
         <v>Master</v>
       </c>
       <c r="V318" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="319">
@@ -22093,7 +22093,7 @@
         <v>Master</v>
       </c>
       <c r="V319" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="320">
@@ -22161,7 +22161,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V320" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="321">
@@ -22229,7 +22229,7 @@
         <v>Master</v>
       </c>
       <c r="V321" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="322">
@@ -22365,7 +22365,7 @@
         <v>Master</v>
       </c>
       <c r="V323" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="324">
@@ -22433,7 +22433,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V324" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="325">
@@ -22501,7 +22501,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V325" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="326">
@@ -22569,7 +22569,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V326" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="327">
@@ -22705,7 +22705,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V328" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="329">
@@ -22773,7 +22773,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V329" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="330">
@@ -22841,7 +22841,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V330" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="331">
@@ -22909,7 +22909,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V331" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.539Z</v>
       </c>
     </row>
     <row r="332">
@@ -22977,7 +22977,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V332" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="333">
@@ -23045,7 +23045,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V333" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="334">
@@ -23113,7 +23113,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V334" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="335">
@@ -23181,7 +23181,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V335" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="336">
@@ -23249,7 +23249,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V336" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="337">
@@ -23317,7 +23317,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V337" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="338">
@@ -23385,7 +23385,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V338" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="339">
@@ -23453,7 +23453,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V339" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="340">
@@ -23521,7 +23521,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V340" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="341">
@@ -23589,7 +23589,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V341" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="342">
@@ -23657,7 +23657,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V342" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="343">
@@ -23725,7 +23725,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V343" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="344">
@@ -23793,7 +23793,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V344" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="345">
@@ -23861,7 +23861,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V345" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="346">
@@ -23929,7 +23929,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V346" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="347">
@@ -23997,7 +23997,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V347" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="348">
@@ -24065,7 +24065,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V348" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="349">
@@ -24133,7 +24133,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V349" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="350">
@@ -24201,7 +24201,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V350" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="351">
@@ -24269,7 +24269,7 @@
         <v>Master</v>
       </c>
       <c r="V351" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="352">
@@ -24337,7 +24337,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V352" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="353">
@@ -24405,7 +24405,7 @@
         <v>Master</v>
       </c>
       <c r="V353" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="354">
@@ -24473,7 +24473,7 @@
         <v>Master</v>
       </c>
       <c r="V354" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="355">
@@ -24541,7 +24541,7 @@
         <v>Master</v>
       </c>
       <c r="V355" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="356">
@@ -24609,7 +24609,7 @@
         <v>Master</v>
       </c>
       <c r="V356" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="357">
@@ -24677,7 +24677,7 @@
         <v>Master</v>
       </c>
       <c r="V357" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="358">
@@ -24745,7 +24745,7 @@
         <v>Master</v>
       </c>
       <c r="V358" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="359">
@@ -24813,7 +24813,7 @@
         <v>Master</v>
       </c>
       <c r="V359" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="360">
@@ -24881,7 +24881,7 @@
         <v>دليل الإيجارات</v>
       </c>
       <c r="V360" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="361">
@@ -25017,7 +25017,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V362" t="str">
-        <v>2026-09-04T14:50:11.475Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="363">
@@ -25085,7 +25085,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V363" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="364">
@@ -25153,7 +25153,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V364" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="365">
@@ -25289,7 +25289,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V366" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="367">
@@ -25357,7 +25357,7 @@
         <v>Available Properties</v>
       </c>
       <c r="V367" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="368">
@@ -25493,7 +25493,7 @@
         <v>Master</v>
       </c>
       <c r="V369" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="370">
@@ -25561,7 +25561,7 @@
         <v>Master</v>
       </c>
       <c r="V370" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="371">
@@ -25697,7 +25697,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V372" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="373">
@@ -25765,7 +25765,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V373" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="374">
@@ -25901,7 +25901,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V375" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="376">
@@ -25969,7 +25969,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V376" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="377">
@@ -26037,7 +26037,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V377" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="378">
@@ -26173,7 +26173,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V379" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="380">
@@ -26241,7 +26241,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V380" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="381">
@@ -26309,7 +26309,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V381" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="382">
@@ -26377,7 +26377,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V382" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="383">
@@ -26445,7 +26445,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V383" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="384">
@@ -26513,7 +26513,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V384" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="385">
@@ -26581,7 +26581,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V385" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="386">
@@ -26649,7 +26649,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V386" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="387">
@@ -26717,7 +26717,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V387" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="388">
@@ -26785,7 +26785,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V388" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="389">
@@ -26853,7 +26853,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V389" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="390">
@@ -26921,7 +26921,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V390" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="391">
@@ -26989,7 +26989,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V391" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="392">
@@ -27057,7 +27057,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V392" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="393">
@@ -27125,7 +27125,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V393" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="394">
@@ -28009,7 +28009,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V406" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="407">
@@ -28553,7 +28553,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V414" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="415">
@@ -28621,7 +28621,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V415" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="416">
@@ -28825,7 +28825,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V418" t="str">
-        <v>2026-09-04T14:50:11.476Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="419">
@@ -36305,7 +36305,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V528" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="529">
@@ -36373,7 +36373,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V529" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="530">
@@ -36441,7 +36441,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V530" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="531">
@@ -36509,7 +36509,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V531" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="532">
@@ -36577,7 +36577,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V532" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="533">
@@ -36645,7 +36645,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V533" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="534">
@@ -36713,7 +36713,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V534" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="535">
@@ -36781,7 +36781,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V535" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="536">
@@ -36849,7 +36849,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V536" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="537">
@@ -36917,7 +36917,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V537" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="538">
@@ -36985,7 +36985,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V538" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="539">
@@ -37053,7 +37053,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V539" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="540">
@@ -37121,7 +37121,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V540" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="541">
@@ -37189,7 +37189,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V541" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="542">
@@ -37257,7 +37257,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V542" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="543">
@@ -37325,7 +37325,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V543" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="544">
@@ -37461,7 +37461,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V545" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="546">
@@ -37529,7 +37529,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V546" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="547">
@@ -37597,7 +37597,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V547" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="548">
@@ -37665,7 +37665,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V548" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="549">
@@ -37869,7 +37869,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V551" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="552">
@@ -38073,7 +38073,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V554" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="555">
@@ -38141,7 +38141,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V555" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="556">
@@ -38345,7 +38345,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V558" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="559">
@@ -38481,7 +38481,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V560" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="561">
@@ -38549,7 +38549,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V561" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="562">
@@ -38617,7 +38617,7 @@
         <v>Comprehensive Inventory</v>
       </c>
       <c r="V562" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="563">
@@ -39025,7 +39025,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V568" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="569">
@@ -39093,7 +39093,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V569" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="570">
@@ -39161,7 +39161,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V570" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="571">
@@ -39229,7 +39229,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V571" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="572">
@@ -39297,7 +39297,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V572" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="573">
@@ -39365,7 +39365,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V573" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="574">
@@ -39433,7 +39433,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V574" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="575">
@@ -39501,7 +39501,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V575" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="576">
@@ -39569,7 +39569,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V576" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="577">
@@ -39637,7 +39637,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V577" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="578">
@@ -39705,7 +39705,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V578" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="579">
@@ -39773,7 +39773,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V579" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="580">
@@ -39841,7 +39841,7 @@
         <v>Dashboard</v>
       </c>
       <c r="V580" t="str">
-        <v>2026-09-04T14:50:11.477Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="581">
@@ -42085,7 +42085,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V613" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="614" xml:space="preserve">
@@ -42154,7 +42154,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V614" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="615">
@@ -42222,7 +42222,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V615" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="616">
@@ -42290,7 +42290,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V616" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="617">
@@ -42358,7 +42358,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V617" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="618">
@@ -42426,7 +42426,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V618" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="619">
@@ -42494,7 +42494,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V619" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.540Z</v>
       </c>
     </row>
     <row r="620">
@@ -42562,7 +42562,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V620" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.541Z</v>
       </c>
     </row>
     <row r="621">
@@ -42630,7 +42630,7 @@
         <v>Broker / group</v>
       </c>
       <c r="V621" t="str">
-        <v>2026-09-04T14:50:11.478Z</v>
+        <v>2026-09-07T03:58:05.541Z</v>
       </c>
     </row>
   </sheetData>
